--- a/project-omakase/30_管理/01_収支計画モデル.xlsx
+++ b/project-omakase/30_管理/01_収支計画モデル.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="前提条件" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="月次_保守" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="月次_標準" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="月次_強気" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="年次サマリ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="KPI実績入力" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提条件" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次_保守" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次_標準" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月次_強気" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年次サマリ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI実績入力" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -586,14 +586,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>海外向け日本グルメメディア事業　収支計画モデル（36ヶ月・3シナリオ）</t>
+          <t>海外向け 日本家庭料理メディア事業　収支計画モデル（36ヶ月・3シナリオ）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>作成日 2026年7月27日 ／ 通貨単位：円（$建て商品は為替レートで換算）</t>
+          <t>v2（2026年7月28日・家庭料理モデル）／ 通貨単位：円（$建て商品は為替レートで換算）</t>
         </is>
       </c>
     </row>
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B21" s="8" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>1500</v>
       </c>
       <c r="D21" s="8" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -775,13 +775,13 @@
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B23" s="8" t="n">
-        <v>900</v>
+        <v>1100</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>3500</v>
+        <v>3600</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>11000</v>
+        <v>11500</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -853,13 +853,13 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>6000</v>
+        <v>6300</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>13000</v>
+        <v>13500</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
@@ -956,24 +956,24 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>③ デジタルガイド販売</t>
+          <t>③ レシピデジタル商品</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>ガイド価格（〜12ヶ月目）</t>
+          <t>レシピ商品 価格（〜12ヶ月目）</t>
         </is>
       </c>
       <c r="B31" s="8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C31" s="8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D31" s="8" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Tokyo Access Guide 単品</t>
+          <t>Weeknight Japanese（60レシピ＋食材置換表）</t>
         </is>
       </c>
     </row>
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C32" s="8" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D32" s="8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>バンドル$39の構成比上昇を反映</t>
+          <t>バンドル$45と訪日商品$19の構成を反映</t>
         </is>
       </c>
     </row>
@@ -1019,13 +1019,13 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>無料PDF登録者→$19商品。5〜10%が実務水準</t>
+          <t>レシピ観客にレシピ商品を売るため v1(8%)より高い</t>
         </is>
       </c>
     </row>
@@ -1045,13 +1045,13 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.0015</v>
+        <v>0.002</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>0.0025</v>
+        <v>0.003</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
@@ -1071,13 +1071,13 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>0.02</v>
+        <v>0.022</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>④ アフィリエイト</t>
+          <t>④ アフィリエイト（食材・調理器具）</t>
         </is>
       </c>
     </row>
@@ -1156,13 +1156,13 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="C39" s="13" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
@@ -1171,14 +1171,14 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Klook・GetYourGuide・eSIM等の合算</t>
+          <t>Amazon各国・日本食材EC・包丁等。季節性なし</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>⑤ 店舗・DMOタイアップ</t>
+          <t>⑤ 日本食ブランドのタイアップ</t>
         </is>
       </c>
     </row>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="B41" s="8" t="n">
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="C41" s="8" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="D41" s="8" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>実績データ（来店計測）の有無で単価が決まる</t>
+          <t>アフィリ実売数を示せるかで単価が2〜3倍変わる</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>⑥ Itinerary Review（旅程レビュー）</t>
+          <t>⑥ 訪日セグメント向け商品（15ヶ月目〜）</t>
         </is>
       </c>
     </row>
@@ -1310,13 +1310,13 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C47" s="8" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="D47" s="8" t="n">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -1325,105 +1325,113 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>13ヶ月目〜</t>
+          <t>訪日予定層にのみ販売（15ヶ月目〜）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>新規購読者の申込率</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="C48" s="12" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D48" s="12" t="n">
+          <t>新規購読者×訪日比率×転換率</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C48" s="11" t="n">
         <v>0.025</v>
       </c>
+      <c r="D48" s="11" t="n">
+        <v>0.045</v>
+      </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr"/>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>3ヶ月目に訪日比率を実測して更新すること</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>⑦ 運用代行（BtoB・19ヶ月目〜）</t>
+          <t>⑦ 予約代行（20ヶ月目〜・任意）</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>月額単価</t>
+          <t>月間粗利</t>
         </is>
       </c>
       <c r="B50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="D50" s="8" t="n">
         <v>150000</v>
       </c>
-      <c r="C50" s="8" t="n">
-        <v>250000</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>350000</v>
-      </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>円/社/月</t>
+          <t>円/月</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>料理系クリエイターの海外チャンネル運用</t>
+          <t>レストラン予約のみ＝旅行業登録不要。月10件上限</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>受託社数：19〜24ヶ月目</t>
+          <t>稼働係数：19〜24ヶ月目</t>
         </is>
       </c>
       <c r="B51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="C51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>社</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr"/>
+          <t>係数</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>訪日セグメントが育った場合のみ</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>受託社数：25〜36ヶ月目</t>
+          <t>稼働係数：25〜36ヶ月目</t>
         </is>
       </c>
       <c r="B52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C52" s="8" t="n">
-        <v>2</v>
-      </c>
       <c r="D52" s="8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>社</t>
+          <t>係数</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr"/>
@@ -1438,17 +1446,17 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>取材費：1〜6ヶ月目</t>
+          <t>食材費：1〜6ヶ月目</t>
         </is>
       </c>
       <c r="B54" s="8" t="n">
-        <v>30000</v>
+        <v>18000</v>
       </c>
       <c r="C54" s="8" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="D54" s="8" t="n">
-        <v>50000</v>
+        <v>32000</v>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
@@ -1457,46 +1465,50 @@
       </c>
       <c r="F54" s="9" t="inlineStr">
         <is>
-          <t>飲食代＋交通費。月20〜25店</t>
+          <t>週末まとめ撮り 3〜4品／週</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>取材費：7〜18ヶ月目</t>
+          <t>食材費：7〜18ヶ月目</t>
         </is>
       </c>
       <c r="B55" s="8" t="n">
-        <v>45000</v>
+        <v>25000</v>
       </c>
       <c r="C55" s="8" t="n">
-        <v>60000</v>
+        <v>35000</v>
       </c>
       <c r="D55" s="8" t="n">
-        <v>80000</v>
+        <v>48000</v>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
           <t>円/月</t>
         </is>
       </c>
-      <c r="F55" s="9" t="inlineStr"/>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>検証用の代替食材を含む</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>取材費：19〜36ヶ月目</t>
+          <t>食材費：19〜36ヶ月目</t>
         </is>
       </c>
       <c r="B56" s="8" t="n">
-        <v>60000</v>
+        <v>32000</v>
       </c>
       <c r="C56" s="8" t="n">
-        <v>80000</v>
+        <v>45000</v>
       </c>
       <c r="D56" s="8" t="n">
-        <v>120000</v>
+        <v>65000</v>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
@@ -1830,13 +1842,13 @@
         </is>
       </c>
       <c r="B70" s="8" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="C70" s="8" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="D70" s="8" t="n">
-        <v>200000</v>
+        <v>120000</v>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
@@ -1845,7 +1857,7 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>撮影機材15万＋LP/ドメイン5万</t>
+          <t>撮影機材7万＋調理器具3万＋LP2万</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2000,7 @@
       </c>
       <c r="N4" s="15" t="inlineStr">
         <is>
-          <t>ガイド売上</t>
+          <t>レシピ商品</t>
         </is>
       </c>
       <c r="O4" s="15" t="inlineStr">
@@ -2003,12 +2015,12 @@
       </c>
       <c r="Q4" s="15" t="inlineStr">
         <is>
-          <t>ｺﾝｼｪﾙｼﾞｭ</t>
+          <t>訪日商品</t>
         </is>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
-          <t>運用代行</t>
+          <t>予約代行</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
@@ -2018,7 +2030,7 @@
       </c>
       <c r="T4" s="15" t="inlineStr">
         <is>
-          <t>取材費</t>
+          <t>食材費</t>
         </is>
       </c>
       <c r="U4" s="15" t="inlineStr">
@@ -2112,7 +2124,7 @@
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>IF(OR($A5=5,$A5=9,$A5=15,$A5=21,$A5=27,$A5=33),ROUND(0*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A5=5,$A5=11,$A5=15,$A5=22,$A5=30),ROUND(0*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L5" s="16">
@@ -2136,11 +2148,11 @@
         <v/>
       </c>
       <c r="Q5" s="16">
-        <f>IF($A5&lt;13,0,ROUND($G5*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A5&lt;15,0,ROUND($G5*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R5" s="16">
-        <f>IF($A5&lt;19,0,IF($A5&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A5&lt;20,0,IF($A5&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S5" s="16">
@@ -2233,7 +2245,7 @@
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>IF(OR($A6=5,$A6=9,$A6=15,$A6=21,$A6=27,$A6=33),ROUND($I5*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A6=5,$A6=11,$A6=15,$A6=22,$A6=30),ROUND($I5*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L6" s="16">
@@ -2257,11 +2269,11 @@
         <v/>
       </c>
       <c r="Q6" s="16">
-        <f>IF($A6&lt;13,0,ROUND($G6*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A6&lt;15,0,ROUND($G6*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R6" s="16">
-        <f>IF($A6&lt;19,0,IF($A6&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A6&lt;20,0,IF($A6&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S6" s="16">
@@ -2354,7 +2366,7 @@
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>IF(OR($A7=5,$A7=9,$A7=15,$A7=21,$A7=27,$A7=33),ROUND($I6*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A7=5,$A7=11,$A7=15,$A7=22,$A7=30),ROUND($I6*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L7" s="16">
@@ -2378,11 +2390,11 @@
         <v/>
       </c>
       <c r="Q7" s="16">
-        <f>IF($A7&lt;13,0,ROUND($G7*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A7&lt;15,0,ROUND($G7*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R7" s="16">
-        <f>IF($A7&lt;19,0,IF($A7&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A7&lt;20,0,IF($A7&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S7" s="16">
@@ -2475,7 +2487,7 @@
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>IF(OR($A8=5,$A8=9,$A8=15,$A8=21,$A8=27,$A8=33),ROUND($I7*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A8=5,$A8=11,$A8=15,$A8=22,$A8=30),ROUND($I7*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L8" s="16">
@@ -2499,11 +2511,11 @@
         <v/>
       </c>
       <c r="Q8" s="16">
-        <f>IF($A8&lt;13,0,ROUND($G8*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A8&lt;15,0,ROUND($G8*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R8" s="16">
-        <f>IF($A8&lt;19,0,IF($A8&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A8&lt;20,0,IF($A8&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S8" s="16">
@@ -2596,7 +2608,7 @@
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>IF(OR($A9=5,$A9=9,$A9=15,$A9=21,$A9=27,$A9=33),ROUND($I8*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A9=5,$A9=11,$A9=15,$A9=22,$A9=30),ROUND($I8*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L9" s="16">
@@ -2620,11 +2632,11 @@
         <v/>
       </c>
       <c r="Q9" s="16">
-        <f>IF($A9&lt;13,0,ROUND($G9*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A9&lt;15,0,ROUND($G9*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R9" s="16">
-        <f>IF($A9&lt;19,0,IF($A9&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A9&lt;20,0,IF($A9&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S9" s="16">
@@ -2717,7 +2729,7 @@
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>IF(OR($A10=5,$A10=9,$A10=15,$A10=21,$A10=27,$A10=33),ROUND($I9*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A10=5,$A10=11,$A10=15,$A10=22,$A10=30),ROUND($I9*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L10" s="16">
@@ -2741,11 +2753,11 @@
         <v/>
       </c>
       <c r="Q10" s="16">
-        <f>IF($A10&lt;13,0,ROUND($G10*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A10&lt;15,0,ROUND($G10*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R10" s="16">
-        <f>IF($A10&lt;19,0,IF($A10&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A10&lt;20,0,IF($A10&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S10" s="16">
@@ -2838,7 +2850,7 @@
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>IF(OR($A11=5,$A11=9,$A11=15,$A11=21,$A11=27,$A11=33),ROUND($I10*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A11=5,$A11=11,$A11=15,$A11=22,$A11=30),ROUND($I10*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L11" s="16">
@@ -2862,11 +2874,11 @@
         <v/>
       </c>
       <c r="Q11" s="16">
-        <f>IF($A11&lt;13,0,ROUND($G11*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A11&lt;15,0,ROUND($G11*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R11" s="16">
-        <f>IF($A11&lt;19,0,IF($A11&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A11&lt;20,0,IF($A11&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S11" s="16">
@@ -2959,7 +2971,7 @@
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>IF(OR($A12=5,$A12=9,$A12=15,$A12=21,$A12=27,$A12=33),ROUND($I11*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A12=5,$A12=11,$A12=15,$A12=22,$A12=30),ROUND($I11*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L12" s="16">
@@ -2983,11 +2995,11 @@
         <v/>
       </c>
       <c r="Q12" s="16">
-        <f>IF($A12&lt;13,0,ROUND($G12*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A12&lt;15,0,ROUND($G12*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R12" s="16">
-        <f>IF($A12&lt;19,0,IF($A12&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A12&lt;20,0,IF($A12&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S12" s="16">
@@ -3080,7 +3092,7 @@
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>IF(OR($A13=5,$A13=9,$A13=15,$A13=21,$A13=27,$A13=33),ROUND($I12*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A13=5,$A13=11,$A13=15,$A13=22,$A13=30),ROUND($I12*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L13" s="16">
@@ -3104,11 +3116,11 @@
         <v/>
       </c>
       <c r="Q13" s="16">
-        <f>IF($A13&lt;13,0,ROUND($G13*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A13&lt;15,0,ROUND($G13*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R13" s="16">
-        <f>IF($A13&lt;19,0,IF($A13&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A13&lt;20,0,IF($A13&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S13" s="16">
@@ -3201,7 +3213,7 @@
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>IF(OR($A14=5,$A14=9,$A14=15,$A14=21,$A14=27,$A14=33),ROUND($I13*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A14=5,$A14=11,$A14=15,$A14=22,$A14=30),ROUND($I13*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L14" s="16">
@@ -3225,11 +3237,11 @@
         <v/>
       </c>
       <c r="Q14" s="16">
-        <f>IF($A14&lt;13,0,ROUND($G14*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A14&lt;15,0,ROUND($G14*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R14" s="16">
-        <f>IF($A14&lt;19,0,IF($A14&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A14&lt;20,0,IF($A14&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S14" s="16">
@@ -3322,7 +3334,7 @@
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>IF(OR($A15=5,$A15=9,$A15=15,$A15=21,$A15=27,$A15=33),ROUND($I14*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A15=5,$A15=11,$A15=15,$A15=22,$A15=30),ROUND($I14*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L15" s="16">
@@ -3346,11 +3358,11 @@
         <v/>
       </c>
       <c r="Q15" s="16">
-        <f>IF($A15&lt;13,0,ROUND($G15*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A15&lt;15,0,ROUND($G15*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R15" s="16">
-        <f>IF($A15&lt;19,0,IF($A15&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A15&lt;20,0,IF($A15&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S15" s="16">
@@ -3443,7 +3455,7 @@
         <v/>
       </c>
       <c r="K16" s="18">
-        <f>IF(OR($A16=5,$A16=9,$A16=15,$A16=21,$A16=27,$A16=33),ROUND($I15*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A16=5,$A16=11,$A16=15,$A16=22,$A16=30),ROUND($I15*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L16" s="18">
@@ -3467,11 +3479,11 @@
         <v/>
       </c>
       <c r="Q16" s="18">
-        <f>IF($A16&lt;13,0,ROUND($G16*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A16&lt;15,0,ROUND($G16*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R16" s="18">
-        <f>IF($A16&lt;19,0,IF($A16&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A16&lt;20,0,IF($A16&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S16" s="18">
@@ -3564,7 +3576,7 @@
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>IF(OR($A17=5,$A17=9,$A17=15,$A17=21,$A17=27,$A17=33),ROUND($I16*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A17=5,$A17=11,$A17=15,$A17=22,$A17=30),ROUND($I16*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L17" s="16">
@@ -3588,11 +3600,11 @@
         <v/>
       </c>
       <c r="Q17" s="16">
-        <f>IF($A17&lt;13,0,ROUND($G17*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A17&lt;15,0,ROUND($G17*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R17" s="16">
-        <f>IF($A17&lt;19,0,IF($A17&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A17&lt;20,0,IF($A17&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S17" s="16">
@@ -3685,7 +3697,7 @@
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>IF(OR($A18=5,$A18=9,$A18=15,$A18=21,$A18=27,$A18=33),ROUND($I17*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A18=5,$A18=11,$A18=15,$A18=22,$A18=30),ROUND($I17*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L18" s="16">
@@ -3709,11 +3721,11 @@
         <v/>
       </c>
       <c r="Q18" s="16">
-        <f>IF($A18&lt;13,0,ROUND($G18*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A18&lt;15,0,ROUND($G18*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R18" s="16">
-        <f>IF($A18&lt;19,0,IF($A18&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A18&lt;20,0,IF($A18&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S18" s="16">
@@ -3806,7 +3818,7 @@
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>IF(OR($A19=5,$A19=9,$A19=15,$A19=21,$A19=27,$A19=33),ROUND($I18*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A19=5,$A19=11,$A19=15,$A19=22,$A19=30),ROUND($I18*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L19" s="16">
@@ -3830,11 +3842,11 @@
         <v/>
       </c>
       <c r="Q19" s="16">
-        <f>IF($A19&lt;13,0,ROUND($G19*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A19&lt;15,0,ROUND($G19*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R19" s="16">
-        <f>IF($A19&lt;19,0,IF($A19&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A19&lt;20,0,IF($A19&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S19" s="16">
@@ -3927,7 +3939,7 @@
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>IF(OR($A20=5,$A20=9,$A20=15,$A20=21,$A20=27,$A20=33),ROUND($I19*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A20=5,$A20=11,$A20=15,$A20=22,$A20=30),ROUND($I19*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L20" s="16">
@@ -3951,11 +3963,11 @@
         <v/>
       </c>
       <c r="Q20" s="16">
-        <f>IF($A20&lt;13,0,ROUND($G20*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A20&lt;15,0,ROUND($G20*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R20" s="16">
-        <f>IF($A20&lt;19,0,IF($A20&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A20&lt;20,0,IF($A20&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S20" s="16">
@@ -4048,7 +4060,7 @@
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>IF(OR($A21=5,$A21=9,$A21=15,$A21=21,$A21=27,$A21=33),ROUND($I20*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A21=5,$A21=11,$A21=15,$A21=22,$A21=30),ROUND($I20*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L21" s="16">
@@ -4072,11 +4084,11 @@
         <v/>
       </c>
       <c r="Q21" s="16">
-        <f>IF($A21&lt;13,0,ROUND($G21*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A21&lt;15,0,ROUND($G21*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R21" s="16">
-        <f>IF($A21&lt;19,0,IF($A21&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A21&lt;20,0,IF($A21&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S21" s="16">
@@ -4169,7 +4181,7 @@
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>IF(OR($A22=5,$A22=9,$A22=15,$A22=21,$A22=27,$A22=33),ROUND($I21*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A22=5,$A22=11,$A22=15,$A22=22,$A22=30),ROUND($I21*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L22" s="16">
@@ -4193,11 +4205,11 @@
         <v/>
       </c>
       <c r="Q22" s="16">
-        <f>IF($A22&lt;13,0,ROUND($G22*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A22&lt;15,0,ROUND($G22*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R22" s="16">
-        <f>IF($A22&lt;19,0,IF($A22&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A22&lt;20,0,IF($A22&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S22" s="16">
@@ -4290,7 +4302,7 @@
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>IF(OR($A23=5,$A23=9,$A23=15,$A23=21,$A23=27,$A23=33),ROUND($I22*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A23=5,$A23=11,$A23=15,$A23=22,$A23=30),ROUND($I22*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L23" s="16">
@@ -4314,11 +4326,11 @@
         <v/>
       </c>
       <c r="Q23" s="16">
-        <f>IF($A23&lt;13,0,ROUND($G23*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A23&lt;15,0,ROUND($G23*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R23" s="16">
-        <f>IF($A23&lt;19,0,IF($A23&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A23&lt;20,0,IF($A23&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S23" s="16">
@@ -4411,7 +4423,7 @@
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>IF(OR($A24=5,$A24=9,$A24=15,$A24=21,$A24=27,$A24=33),ROUND($I23*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A24=5,$A24=11,$A24=15,$A24=22,$A24=30),ROUND($I23*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L24" s="16">
@@ -4435,11 +4447,11 @@
         <v/>
       </c>
       <c r="Q24" s="16">
-        <f>IF($A24&lt;13,0,ROUND($G24*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A24&lt;15,0,ROUND($G24*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R24" s="16">
-        <f>IF($A24&lt;19,0,IF($A24&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A24&lt;20,0,IF($A24&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S24" s="16">
@@ -4532,7 +4544,7 @@
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>IF(OR($A25=5,$A25=9,$A25=15,$A25=21,$A25=27,$A25=33),ROUND($I24*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A25=5,$A25=11,$A25=15,$A25=22,$A25=30),ROUND($I24*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L25" s="16">
@@ -4556,11 +4568,11 @@
         <v/>
       </c>
       <c r="Q25" s="16">
-        <f>IF($A25&lt;13,0,ROUND($G25*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A25&lt;15,0,ROUND($G25*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R25" s="16">
-        <f>IF($A25&lt;19,0,IF($A25&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A25&lt;20,0,IF($A25&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S25" s="16">
@@ -4653,7 +4665,7 @@
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>IF(OR($A26=5,$A26=9,$A26=15,$A26=21,$A26=27,$A26=33),ROUND($I25*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A26=5,$A26=11,$A26=15,$A26=22,$A26=30),ROUND($I25*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L26" s="16">
@@ -4677,11 +4689,11 @@
         <v/>
       </c>
       <c r="Q26" s="16">
-        <f>IF($A26&lt;13,0,ROUND($G26*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A26&lt;15,0,ROUND($G26*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R26" s="16">
-        <f>IF($A26&lt;19,0,IF($A26&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A26&lt;20,0,IF($A26&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S26" s="16">
@@ -4774,7 +4786,7 @@
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>IF(OR($A27=5,$A27=9,$A27=15,$A27=21,$A27=27,$A27=33),ROUND($I26*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A27=5,$A27=11,$A27=15,$A27=22,$A27=30),ROUND($I26*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L27" s="16">
@@ -4798,11 +4810,11 @@
         <v/>
       </c>
       <c r="Q27" s="16">
-        <f>IF($A27&lt;13,0,ROUND($G27*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A27&lt;15,0,ROUND($G27*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R27" s="16">
-        <f>IF($A27&lt;19,0,IF($A27&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A27&lt;20,0,IF($A27&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S27" s="16">
@@ -4895,7 +4907,7 @@
         <v/>
       </c>
       <c r="K28" s="18">
-        <f>IF(OR($A28=5,$A28=9,$A28=15,$A28=21,$A28=27,$A28=33),ROUND($I27*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A28=5,$A28=11,$A28=15,$A28=22,$A28=30),ROUND($I27*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L28" s="18">
@@ -4919,11 +4931,11 @@
         <v/>
       </c>
       <c r="Q28" s="18">
-        <f>IF($A28&lt;13,0,ROUND($G28*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A28&lt;15,0,ROUND($G28*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R28" s="18">
-        <f>IF($A28&lt;19,0,IF($A28&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A28&lt;20,0,IF($A28&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S28" s="18">
@@ -5016,7 +5028,7 @@
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>IF(OR($A29=5,$A29=9,$A29=15,$A29=21,$A29=27,$A29=33),ROUND($I28*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A29=5,$A29=11,$A29=15,$A29=22,$A29=30),ROUND($I28*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L29" s="16">
@@ -5040,11 +5052,11 @@
         <v/>
       </c>
       <c r="Q29" s="16">
-        <f>IF($A29&lt;13,0,ROUND($G29*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A29&lt;15,0,ROUND($G29*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R29" s="16">
-        <f>IF($A29&lt;19,0,IF($A29&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A29&lt;20,0,IF($A29&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S29" s="16">
@@ -5137,7 +5149,7 @@
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>IF(OR($A30=5,$A30=9,$A30=15,$A30=21,$A30=27,$A30=33),ROUND($I29*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A30=5,$A30=11,$A30=15,$A30=22,$A30=30),ROUND($I29*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L30" s="16">
@@ -5161,11 +5173,11 @@
         <v/>
       </c>
       <c r="Q30" s="16">
-        <f>IF($A30&lt;13,0,ROUND($G30*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A30&lt;15,0,ROUND($G30*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R30" s="16">
-        <f>IF($A30&lt;19,0,IF($A30&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A30&lt;20,0,IF($A30&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S30" s="16">
@@ -5258,7 +5270,7 @@
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>IF(OR($A31=5,$A31=9,$A31=15,$A31=21,$A31=27,$A31=33),ROUND($I30*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A31=5,$A31=11,$A31=15,$A31=22,$A31=30),ROUND($I30*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L31" s="16">
@@ -5282,11 +5294,11 @@
         <v/>
       </c>
       <c r="Q31" s="16">
-        <f>IF($A31&lt;13,0,ROUND($G31*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A31&lt;15,0,ROUND($G31*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R31" s="16">
-        <f>IF($A31&lt;19,0,IF($A31&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A31&lt;20,0,IF($A31&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S31" s="16">
@@ -5379,7 +5391,7 @@
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>IF(OR($A32=5,$A32=9,$A32=15,$A32=21,$A32=27,$A32=33),ROUND($I31*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A32=5,$A32=11,$A32=15,$A32=22,$A32=30),ROUND($I31*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L32" s="16">
@@ -5403,11 +5415,11 @@
         <v/>
       </c>
       <c r="Q32" s="16">
-        <f>IF($A32&lt;13,0,ROUND($G32*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A32&lt;15,0,ROUND($G32*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R32" s="16">
-        <f>IF($A32&lt;19,0,IF($A32&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A32&lt;20,0,IF($A32&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S32" s="16">
@@ -5500,7 +5512,7 @@
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>IF(OR($A33=5,$A33=9,$A33=15,$A33=21,$A33=27,$A33=33),ROUND($I32*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A33=5,$A33=11,$A33=15,$A33=22,$A33=30),ROUND($I32*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L33" s="16">
@@ -5524,11 +5536,11 @@
         <v/>
       </c>
       <c r="Q33" s="16">
-        <f>IF($A33&lt;13,0,ROUND($G33*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A33&lt;15,0,ROUND($G33*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R33" s="16">
-        <f>IF($A33&lt;19,0,IF($A33&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A33&lt;20,0,IF($A33&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S33" s="16">
@@ -5621,7 +5633,7 @@
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>IF(OR($A34=5,$A34=9,$A34=15,$A34=21,$A34=27,$A34=33),ROUND($I33*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A34=5,$A34=11,$A34=15,$A34=22,$A34=30),ROUND($I33*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L34" s="16">
@@ -5645,11 +5657,11 @@
         <v/>
       </c>
       <c r="Q34" s="16">
-        <f>IF($A34&lt;13,0,ROUND($G34*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A34&lt;15,0,ROUND($G34*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R34" s="16">
-        <f>IF($A34&lt;19,0,IF($A34&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A34&lt;20,0,IF($A34&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S34" s="16">
@@ -5742,7 +5754,7 @@
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>IF(OR($A35=5,$A35=9,$A35=15,$A35=21,$A35=27,$A35=33),ROUND($I34*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A35=5,$A35=11,$A35=15,$A35=22,$A35=30),ROUND($I34*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L35" s="16">
@@ -5766,11 +5778,11 @@
         <v/>
       </c>
       <c r="Q35" s="16">
-        <f>IF($A35&lt;13,0,ROUND($G35*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A35&lt;15,0,ROUND($G35*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R35" s="16">
-        <f>IF($A35&lt;19,0,IF($A35&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A35&lt;20,0,IF($A35&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S35" s="16">
@@ -5863,7 +5875,7 @@
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>IF(OR($A36=5,$A36=9,$A36=15,$A36=21,$A36=27,$A36=33),ROUND($I35*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A36=5,$A36=11,$A36=15,$A36=22,$A36=30),ROUND($I35*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L36" s="16">
@@ -5887,11 +5899,11 @@
         <v/>
       </c>
       <c r="Q36" s="16">
-        <f>IF($A36&lt;13,0,ROUND($G36*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A36&lt;15,0,ROUND($G36*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R36" s="16">
-        <f>IF($A36&lt;19,0,IF($A36&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A36&lt;20,0,IF($A36&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S36" s="16">
@@ -5984,7 +5996,7 @@
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>IF(OR($A37=5,$A37=9,$A37=15,$A37=21,$A37=27,$A37=33),ROUND($I36*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A37=5,$A37=11,$A37=15,$A37=22,$A37=30),ROUND($I36*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L37" s="16">
@@ -6008,11 +6020,11 @@
         <v/>
       </c>
       <c r="Q37" s="16">
-        <f>IF($A37&lt;13,0,ROUND($G37*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A37&lt;15,0,ROUND($G37*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R37" s="16">
-        <f>IF($A37&lt;19,0,IF($A37&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A37&lt;20,0,IF($A37&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S37" s="16">
@@ -6105,7 +6117,7 @@
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF(OR($A38=5,$A38=9,$A38=15,$A38=21,$A38=27,$A38=33),ROUND($I37*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A38=5,$A38=11,$A38=15,$A38=22,$A38=30),ROUND($I37*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L38" s="16">
@@ -6129,11 +6141,11 @@
         <v/>
       </c>
       <c r="Q38" s="16">
-        <f>IF($A38&lt;13,0,ROUND($G38*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A38&lt;15,0,ROUND($G38*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R38" s="16">
-        <f>IF($A38&lt;19,0,IF($A38&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A38&lt;20,0,IF($A38&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S38" s="16">
@@ -6226,7 +6238,7 @@
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>IF(OR($A39=5,$A39=9,$A39=15,$A39=21,$A39=27,$A39=33),ROUND($I38*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A39=5,$A39=11,$A39=15,$A39=22,$A39=30),ROUND($I38*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L39" s="16">
@@ -6250,11 +6262,11 @@
         <v/>
       </c>
       <c r="Q39" s="16">
-        <f>IF($A39&lt;13,0,ROUND($G39*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A39&lt;15,0,ROUND($G39*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R39" s="16">
-        <f>IF($A39&lt;19,0,IF($A39&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A39&lt;20,0,IF($A39&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S39" s="16">
@@ -6347,7 +6359,7 @@
         <v/>
       </c>
       <c r="K40" s="18">
-        <f>IF(OR($A40=5,$A40=9,$A40=15,$A40=21,$A40=27,$A40=33),ROUND($I39*前提条件!$B$35,0),0)</f>
+        <f>IF(OR($A40=5,$A40=11,$A40=15,$A40=22,$A40=30),ROUND($I39*前提条件!$B$35,0),0)</f>
         <v/>
       </c>
       <c r="L40" s="18">
@@ -6371,11 +6383,11 @@
         <v/>
       </c>
       <c r="Q40" s="18">
-        <f>IF($A40&lt;13,0,ROUND($G40*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
+        <f>IF($A40&lt;15,0,ROUND($G40*前提条件!$B$48*前提条件!$B$47*前提条件!$B$19,0))</f>
         <v/>
       </c>
       <c r="R40" s="18">
-        <f>IF($A40&lt;19,0,IF($A40&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
+        <f>IF($A40&lt;20,0,IF($A40&lt;=24,前提条件!$B$51,前提条件!$B$52)*前提条件!$B$50)</f>
         <v/>
       </c>
       <c r="S40" s="18">
@@ -6555,7 +6567,7 @@
       </c>
       <c r="N4" s="15" t="inlineStr">
         <is>
-          <t>ガイド売上</t>
+          <t>レシピ商品</t>
         </is>
       </c>
       <c r="O4" s="15" t="inlineStr">
@@ -6570,12 +6582,12 @@
       </c>
       <c r="Q4" s="15" t="inlineStr">
         <is>
-          <t>ｺﾝｼｪﾙｼﾞｭ</t>
+          <t>訪日商品</t>
         </is>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
-          <t>運用代行</t>
+          <t>予約代行</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
@@ -6585,7 +6597,7 @@
       </c>
       <c r="T4" s="15" t="inlineStr">
         <is>
-          <t>取材費</t>
+          <t>食材費</t>
         </is>
       </c>
       <c r="U4" s="15" t="inlineStr">
@@ -6679,7 +6691,7 @@
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>IF(OR($A5=5,$A5=9,$A5=15,$A5=21,$A5=27,$A5=33),ROUND(0*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A5=5,$A5=11,$A5=15,$A5=22,$A5=30),ROUND(0*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L5" s="16">
@@ -6703,11 +6715,11 @@
         <v/>
       </c>
       <c r="Q5" s="16">
-        <f>IF($A5&lt;13,0,ROUND($G5*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A5&lt;15,0,ROUND($G5*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R5" s="16">
-        <f>IF($A5&lt;19,0,IF($A5&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A5&lt;20,0,IF($A5&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S5" s="16">
@@ -6800,7 +6812,7 @@
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>IF(OR($A6=5,$A6=9,$A6=15,$A6=21,$A6=27,$A6=33),ROUND($I5*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A6=5,$A6=11,$A6=15,$A6=22,$A6=30),ROUND($I5*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L6" s="16">
@@ -6824,11 +6836,11 @@
         <v/>
       </c>
       <c r="Q6" s="16">
-        <f>IF($A6&lt;13,0,ROUND($G6*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A6&lt;15,0,ROUND($G6*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R6" s="16">
-        <f>IF($A6&lt;19,0,IF($A6&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A6&lt;20,0,IF($A6&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S6" s="16">
@@ -6921,7 +6933,7 @@
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>IF(OR($A7=5,$A7=9,$A7=15,$A7=21,$A7=27,$A7=33),ROUND($I6*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A7=5,$A7=11,$A7=15,$A7=22,$A7=30),ROUND($I6*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L7" s="16">
@@ -6945,11 +6957,11 @@
         <v/>
       </c>
       <c r="Q7" s="16">
-        <f>IF($A7&lt;13,0,ROUND($G7*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A7&lt;15,0,ROUND($G7*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R7" s="16">
-        <f>IF($A7&lt;19,0,IF($A7&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A7&lt;20,0,IF($A7&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S7" s="16">
@@ -7042,7 +7054,7 @@
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>IF(OR($A8=5,$A8=9,$A8=15,$A8=21,$A8=27,$A8=33),ROUND($I7*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A8=5,$A8=11,$A8=15,$A8=22,$A8=30),ROUND($I7*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L8" s="16">
@@ -7066,11 +7078,11 @@
         <v/>
       </c>
       <c r="Q8" s="16">
-        <f>IF($A8&lt;13,0,ROUND($G8*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A8&lt;15,0,ROUND($G8*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R8" s="16">
-        <f>IF($A8&lt;19,0,IF($A8&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A8&lt;20,0,IF($A8&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S8" s="16">
@@ -7163,7 +7175,7 @@
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>IF(OR($A9=5,$A9=9,$A9=15,$A9=21,$A9=27,$A9=33),ROUND($I8*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A9=5,$A9=11,$A9=15,$A9=22,$A9=30),ROUND($I8*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L9" s="16">
@@ -7187,11 +7199,11 @@
         <v/>
       </c>
       <c r="Q9" s="16">
-        <f>IF($A9&lt;13,0,ROUND($G9*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A9&lt;15,0,ROUND($G9*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R9" s="16">
-        <f>IF($A9&lt;19,0,IF($A9&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A9&lt;20,0,IF($A9&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S9" s="16">
@@ -7284,7 +7296,7 @@
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>IF(OR($A10=5,$A10=9,$A10=15,$A10=21,$A10=27,$A10=33),ROUND($I9*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A10=5,$A10=11,$A10=15,$A10=22,$A10=30),ROUND($I9*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L10" s="16">
@@ -7308,11 +7320,11 @@
         <v/>
       </c>
       <c r="Q10" s="16">
-        <f>IF($A10&lt;13,0,ROUND($G10*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A10&lt;15,0,ROUND($G10*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R10" s="16">
-        <f>IF($A10&lt;19,0,IF($A10&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A10&lt;20,0,IF($A10&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S10" s="16">
@@ -7405,7 +7417,7 @@
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>IF(OR($A11=5,$A11=9,$A11=15,$A11=21,$A11=27,$A11=33),ROUND($I10*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A11=5,$A11=11,$A11=15,$A11=22,$A11=30),ROUND($I10*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L11" s="16">
@@ -7429,11 +7441,11 @@
         <v/>
       </c>
       <c r="Q11" s="16">
-        <f>IF($A11&lt;13,0,ROUND($G11*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A11&lt;15,0,ROUND($G11*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R11" s="16">
-        <f>IF($A11&lt;19,0,IF($A11&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A11&lt;20,0,IF($A11&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S11" s="16">
@@ -7526,7 +7538,7 @@
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>IF(OR($A12=5,$A12=9,$A12=15,$A12=21,$A12=27,$A12=33),ROUND($I11*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A12=5,$A12=11,$A12=15,$A12=22,$A12=30),ROUND($I11*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L12" s="16">
@@ -7550,11 +7562,11 @@
         <v/>
       </c>
       <c r="Q12" s="16">
-        <f>IF($A12&lt;13,0,ROUND($G12*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A12&lt;15,0,ROUND($G12*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R12" s="16">
-        <f>IF($A12&lt;19,0,IF($A12&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A12&lt;20,0,IF($A12&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S12" s="16">
@@ -7647,7 +7659,7 @@
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>IF(OR($A13=5,$A13=9,$A13=15,$A13=21,$A13=27,$A13=33),ROUND($I12*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A13=5,$A13=11,$A13=15,$A13=22,$A13=30),ROUND($I12*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L13" s="16">
@@ -7671,11 +7683,11 @@
         <v/>
       </c>
       <c r="Q13" s="16">
-        <f>IF($A13&lt;13,0,ROUND($G13*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A13&lt;15,0,ROUND($G13*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R13" s="16">
-        <f>IF($A13&lt;19,0,IF($A13&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A13&lt;20,0,IF($A13&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S13" s="16">
@@ -7768,7 +7780,7 @@
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>IF(OR($A14=5,$A14=9,$A14=15,$A14=21,$A14=27,$A14=33),ROUND($I13*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A14=5,$A14=11,$A14=15,$A14=22,$A14=30),ROUND($I13*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L14" s="16">
@@ -7792,11 +7804,11 @@
         <v/>
       </c>
       <c r="Q14" s="16">
-        <f>IF($A14&lt;13,0,ROUND($G14*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A14&lt;15,0,ROUND($G14*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R14" s="16">
-        <f>IF($A14&lt;19,0,IF($A14&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A14&lt;20,0,IF($A14&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S14" s="16">
@@ -7889,7 +7901,7 @@
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>IF(OR($A15=5,$A15=9,$A15=15,$A15=21,$A15=27,$A15=33),ROUND($I14*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A15=5,$A15=11,$A15=15,$A15=22,$A15=30),ROUND($I14*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L15" s="16">
@@ -7913,11 +7925,11 @@
         <v/>
       </c>
       <c r="Q15" s="16">
-        <f>IF($A15&lt;13,0,ROUND($G15*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A15&lt;15,0,ROUND($G15*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R15" s="16">
-        <f>IF($A15&lt;19,0,IF($A15&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A15&lt;20,0,IF($A15&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S15" s="16">
@@ -8010,7 +8022,7 @@
         <v/>
       </c>
       <c r="K16" s="18">
-        <f>IF(OR($A16=5,$A16=9,$A16=15,$A16=21,$A16=27,$A16=33),ROUND($I15*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A16=5,$A16=11,$A16=15,$A16=22,$A16=30),ROUND($I15*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L16" s="18">
@@ -8034,11 +8046,11 @@
         <v/>
       </c>
       <c r="Q16" s="18">
-        <f>IF($A16&lt;13,0,ROUND($G16*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A16&lt;15,0,ROUND($G16*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R16" s="18">
-        <f>IF($A16&lt;19,0,IF($A16&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A16&lt;20,0,IF($A16&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S16" s="18">
@@ -8131,7 +8143,7 @@
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>IF(OR($A17=5,$A17=9,$A17=15,$A17=21,$A17=27,$A17=33),ROUND($I16*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A17=5,$A17=11,$A17=15,$A17=22,$A17=30),ROUND($I16*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L17" s="16">
@@ -8155,11 +8167,11 @@
         <v/>
       </c>
       <c r="Q17" s="16">
-        <f>IF($A17&lt;13,0,ROUND($G17*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A17&lt;15,0,ROUND($G17*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R17" s="16">
-        <f>IF($A17&lt;19,0,IF($A17&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A17&lt;20,0,IF($A17&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S17" s="16">
@@ -8252,7 +8264,7 @@
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>IF(OR($A18=5,$A18=9,$A18=15,$A18=21,$A18=27,$A18=33),ROUND($I17*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A18=5,$A18=11,$A18=15,$A18=22,$A18=30),ROUND($I17*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L18" s="16">
@@ -8276,11 +8288,11 @@
         <v/>
       </c>
       <c r="Q18" s="16">
-        <f>IF($A18&lt;13,0,ROUND($G18*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A18&lt;15,0,ROUND($G18*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R18" s="16">
-        <f>IF($A18&lt;19,0,IF($A18&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A18&lt;20,0,IF($A18&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S18" s="16">
@@ -8373,7 +8385,7 @@
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>IF(OR($A19=5,$A19=9,$A19=15,$A19=21,$A19=27,$A19=33),ROUND($I18*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A19=5,$A19=11,$A19=15,$A19=22,$A19=30),ROUND($I18*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L19" s="16">
@@ -8397,11 +8409,11 @@
         <v/>
       </c>
       <c r="Q19" s="16">
-        <f>IF($A19&lt;13,0,ROUND($G19*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A19&lt;15,0,ROUND($G19*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R19" s="16">
-        <f>IF($A19&lt;19,0,IF($A19&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A19&lt;20,0,IF($A19&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S19" s="16">
@@ -8494,7 +8506,7 @@
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>IF(OR($A20=5,$A20=9,$A20=15,$A20=21,$A20=27,$A20=33),ROUND($I19*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A20=5,$A20=11,$A20=15,$A20=22,$A20=30),ROUND($I19*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L20" s="16">
@@ -8518,11 +8530,11 @@
         <v/>
       </c>
       <c r="Q20" s="16">
-        <f>IF($A20&lt;13,0,ROUND($G20*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A20&lt;15,0,ROUND($G20*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R20" s="16">
-        <f>IF($A20&lt;19,0,IF($A20&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A20&lt;20,0,IF($A20&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S20" s="16">
@@ -8615,7 +8627,7 @@
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>IF(OR($A21=5,$A21=9,$A21=15,$A21=21,$A21=27,$A21=33),ROUND($I20*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A21=5,$A21=11,$A21=15,$A21=22,$A21=30),ROUND($I20*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L21" s="16">
@@ -8639,11 +8651,11 @@
         <v/>
       </c>
       <c r="Q21" s="16">
-        <f>IF($A21&lt;13,0,ROUND($G21*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A21&lt;15,0,ROUND($G21*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R21" s="16">
-        <f>IF($A21&lt;19,0,IF($A21&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A21&lt;20,0,IF($A21&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S21" s="16">
@@ -8736,7 +8748,7 @@
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>IF(OR($A22=5,$A22=9,$A22=15,$A22=21,$A22=27,$A22=33),ROUND($I21*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A22=5,$A22=11,$A22=15,$A22=22,$A22=30),ROUND($I21*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L22" s="16">
@@ -8760,11 +8772,11 @@
         <v/>
       </c>
       <c r="Q22" s="16">
-        <f>IF($A22&lt;13,0,ROUND($G22*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A22&lt;15,0,ROUND($G22*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R22" s="16">
-        <f>IF($A22&lt;19,0,IF($A22&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A22&lt;20,0,IF($A22&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S22" s="16">
@@ -8857,7 +8869,7 @@
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>IF(OR($A23=5,$A23=9,$A23=15,$A23=21,$A23=27,$A23=33),ROUND($I22*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A23=5,$A23=11,$A23=15,$A23=22,$A23=30),ROUND($I22*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L23" s="16">
@@ -8881,11 +8893,11 @@
         <v/>
       </c>
       <c r="Q23" s="16">
-        <f>IF($A23&lt;13,0,ROUND($G23*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A23&lt;15,0,ROUND($G23*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R23" s="16">
-        <f>IF($A23&lt;19,0,IF($A23&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A23&lt;20,0,IF($A23&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S23" s="16">
@@ -8978,7 +8990,7 @@
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>IF(OR($A24=5,$A24=9,$A24=15,$A24=21,$A24=27,$A24=33),ROUND($I23*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A24=5,$A24=11,$A24=15,$A24=22,$A24=30),ROUND($I23*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L24" s="16">
@@ -9002,11 +9014,11 @@
         <v/>
       </c>
       <c r="Q24" s="16">
-        <f>IF($A24&lt;13,0,ROUND($G24*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A24&lt;15,0,ROUND($G24*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R24" s="16">
-        <f>IF($A24&lt;19,0,IF($A24&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A24&lt;20,0,IF($A24&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S24" s="16">
@@ -9099,7 +9111,7 @@
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>IF(OR($A25=5,$A25=9,$A25=15,$A25=21,$A25=27,$A25=33),ROUND($I24*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A25=5,$A25=11,$A25=15,$A25=22,$A25=30),ROUND($I24*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L25" s="16">
@@ -9123,11 +9135,11 @@
         <v/>
       </c>
       <c r="Q25" s="16">
-        <f>IF($A25&lt;13,0,ROUND($G25*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A25&lt;15,0,ROUND($G25*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R25" s="16">
-        <f>IF($A25&lt;19,0,IF($A25&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A25&lt;20,0,IF($A25&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S25" s="16">
@@ -9220,7 +9232,7 @@
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>IF(OR($A26=5,$A26=9,$A26=15,$A26=21,$A26=27,$A26=33),ROUND($I25*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A26=5,$A26=11,$A26=15,$A26=22,$A26=30),ROUND($I25*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L26" s="16">
@@ -9244,11 +9256,11 @@
         <v/>
       </c>
       <c r="Q26" s="16">
-        <f>IF($A26&lt;13,0,ROUND($G26*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A26&lt;15,0,ROUND($G26*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R26" s="16">
-        <f>IF($A26&lt;19,0,IF($A26&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A26&lt;20,0,IF($A26&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S26" s="16">
@@ -9341,7 +9353,7 @@
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>IF(OR($A27=5,$A27=9,$A27=15,$A27=21,$A27=27,$A27=33),ROUND($I26*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A27=5,$A27=11,$A27=15,$A27=22,$A27=30),ROUND($I26*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L27" s="16">
@@ -9365,11 +9377,11 @@
         <v/>
       </c>
       <c r="Q27" s="16">
-        <f>IF($A27&lt;13,0,ROUND($G27*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A27&lt;15,0,ROUND($G27*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R27" s="16">
-        <f>IF($A27&lt;19,0,IF($A27&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A27&lt;20,0,IF($A27&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S27" s="16">
@@ -9462,7 +9474,7 @@
         <v/>
       </c>
       <c r="K28" s="18">
-        <f>IF(OR($A28=5,$A28=9,$A28=15,$A28=21,$A28=27,$A28=33),ROUND($I27*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A28=5,$A28=11,$A28=15,$A28=22,$A28=30),ROUND($I27*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L28" s="18">
@@ -9486,11 +9498,11 @@
         <v/>
       </c>
       <c r="Q28" s="18">
-        <f>IF($A28&lt;13,0,ROUND($G28*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A28&lt;15,0,ROUND($G28*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R28" s="18">
-        <f>IF($A28&lt;19,0,IF($A28&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A28&lt;20,0,IF($A28&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S28" s="18">
@@ -9583,7 +9595,7 @@
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>IF(OR($A29=5,$A29=9,$A29=15,$A29=21,$A29=27,$A29=33),ROUND($I28*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A29=5,$A29=11,$A29=15,$A29=22,$A29=30),ROUND($I28*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L29" s="16">
@@ -9607,11 +9619,11 @@
         <v/>
       </c>
       <c r="Q29" s="16">
-        <f>IF($A29&lt;13,0,ROUND($G29*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A29&lt;15,0,ROUND($G29*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R29" s="16">
-        <f>IF($A29&lt;19,0,IF($A29&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A29&lt;20,0,IF($A29&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S29" s="16">
@@ -9704,7 +9716,7 @@
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>IF(OR($A30=5,$A30=9,$A30=15,$A30=21,$A30=27,$A30=33),ROUND($I29*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A30=5,$A30=11,$A30=15,$A30=22,$A30=30),ROUND($I29*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L30" s="16">
@@ -9728,11 +9740,11 @@
         <v/>
       </c>
       <c r="Q30" s="16">
-        <f>IF($A30&lt;13,0,ROUND($G30*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A30&lt;15,0,ROUND($G30*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R30" s="16">
-        <f>IF($A30&lt;19,0,IF($A30&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A30&lt;20,0,IF($A30&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S30" s="16">
@@ -9825,7 +9837,7 @@
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>IF(OR($A31=5,$A31=9,$A31=15,$A31=21,$A31=27,$A31=33),ROUND($I30*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A31=5,$A31=11,$A31=15,$A31=22,$A31=30),ROUND($I30*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L31" s="16">
@@ -9849,11 +9861,11 @@
         <v/>
       </c>
       <c r="Q31" s="16">
-        <f>IF($A31&lt;13,0,ROUND($G31*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A31&lt;15,0,ROUND($G31*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R31" s="16">
-        <f>IF($A31&lt;19,0,IF($A31&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A31&lt;20,0,IF($A31&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S31" s="16">
@@ -9946,7 +9958,7 @@
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>IF(OR($A32=5,$A32=9,$A32=15,$A32=21,$A32=27,$A32=33),ROUND($I31*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A32=5,$A32=11,$A32=15,$A32=22,$A32=30),ROUND($I31*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L32" s="16">
@@ -9970,11 +9982,11 @@
         <v/>
       </c>
       <c r="Q32" s="16">
-        <f>IF($A32&lt;13,0,ROUND($G32*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A32&lt;15,0,ROUND($G32*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R32" s="16">
-        <f>IF($A32&lt;19,0,IF($A32&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A32&lt;20,0,IF($A32&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S32" s="16">
@@ -10067,7 +10079,7 @@
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>IF(OR($A33=5,$A33=9,$A33=15,$A33=21,$A33=27,$A33=33),ROUND($I32*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A33=5,$A33=11,$A33=15,$A33=22,$A33=30),ROUND($I32*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L33" s="16">
@@ -10091,11 +10103,11 @@
         <v/>
       </c>
       <c r="Q33" s="16">
-        <f>IF($A33&lt;13,0,ROUND($G33*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A33&lt;15,0,ROUND($G33*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R33" s="16">
-        <f>IF($A33&lt;19,0,IF($A33&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A33&lt;20,0,IF($A33&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S33" s="16">
@@ -10188,7 +10200,7 @@
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>IF(OR($A34=5,$A34=9,$A34=15,$A34=21,$A34=27,$A34=33),ROUND($I33*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A34=5,$A34=11,$A34=15,$A34=22,$A34=30),ROUND($I33*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L34" s="16">
@@ -10212,11 +10224,11 @@
         <v/>
       </c>
       <c r="Q34" s="16">
-        <f>IF($A34&lt;13,0,ROUND($G34*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A34&lt;15,0,ROUND($G34*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R34" s="16">
-        <f>IF($A34&lt;19,0,IF($A34&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A34&lt;20,0,IF($A34&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S34" s="16">
@@ -10309,7 +10321,7 @@
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>IF(OR($A35=5,$A35=9,$A35=15,$A35=21,$A35=27,$A35=33),ROUND($I34*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A35=5,$A35=11,$A35=15,$A35=22,$A35=30),ROUND($I34*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L35" s="16">
@@ -10333,11 +10345,11 @@
         <v/>
       </c>
       <c r="Q35" s="16">
-        <f>IF($A35&lt;13,0,ROUND($G35*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A35&lt;15,0,ROUND($G35*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R35" s="16">
-        <f>IF($A35&lt;19,0,IF($A35&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A35&lt;20,0,IF($A35&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S35" s="16">
@@ -10430,7 +10442,7 @@
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>IF(OR($A36=5,$A36=9,$A36=15,$A36=21,$A36=27,$A36=33),ROUND($I35*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A36=5,$A36=11,$A36=15,$A36=22,$A36=30),ROUND($I35*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L36" s="16">
@@ -10454,11 +10466,11 @@
         <v/>
       </c>
       <c r="Q36" s="16">
-        <f>IF($A36&lt;13,0,ROUND($G36*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A36&lt;15,0,ROUND($G36*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R36" s="16">
-        <f>IF($A36&lt;19,0,IF($A36&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A36&lt;20,0,IF($A36&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S36" s="16">
@@ -10551,7 +10563,7 @@
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>IF(OR($A37=5,$A37=9,$A37=15,$A37=21,$A37=27,$A37=33),ROUND($I36*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A37=5,$A37=11,$A37=15,$A37=22,$A37=30),ROUND($I36*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L37" s="16">
@@ -10575,11 +10587,11 @@
         <v/>
       </c>
       <c r="Q37" s="16">
-        <f>IF($A37&lt;13,0,ROUND($G37*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A37&lt;15,0,ROUND($G37*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R37" s="16">
-        <f>IF($A37&lt;19,0,IF($A37&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A37&lt;20,0,IF($A37&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S37" s="16">
@@ -10672,7 +10684,7 @@
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF(OR($A38=5,$A38=9,$A38=15,$A38=21,$A38=27,$A38=33),ROUND($I37*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A38=5,$A38=11,$A38=15,$A38=22,$A38=30),ROUND($I37*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L38" s="16">
@@ -10696,11 +10708,11 @@
         <v/>
       </c>
       <c r="Q38" s="16">
-        <f>IF($A38&lt;13,0,ROUND($G38*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A38&lt;15,0,ROUND($G38*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R38" s="16">
-        <f>IF($A38&lt;19,0,IF($A38&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A38&lt;20,0,IF($A38&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S38" s="16">
@@ -10793,7 +10805,7 @@
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>IF(OR($A39=5,$A39=9,$A39=15,$A39=21,$A39=27,$A39=33),ROUND($I38*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A39=5,$A39=11,$A39=15,$A39=22,$A39=30),ROUND($I38*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L39" s="16">
@@ -10817,11 +10829,11 @@
         <v/>
       </c>
       <c r="Q39" s="16">
-        <f>IF($A39&lt;13,0,ROUND($G39*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A39&lt;15,0,ROUND($G39*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R39" s="16">
-        <f>IF($A39&lt;19,0,IF($A39&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A39&lt;20,0,IF($A39&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S39" s="16">
@@ -10914,7 +10926,7 @@
         <v/>
       </c>
       <c r="K40" s="18">
-        <f>IF(OR($A40=5,$A40=9,$A40=15,$A40=21,$A40=27,$A40=33),ROUND($I39*前提条件!$C$35,0),0)</f>
+        <f>IF(OR($A40=5,$A40=11,$A40=15,$A40=22,$A40=30),ROUND($I39*前提条件!$C$35,0),0)</f>
         <v/>
       </c>
       <c r="L40" s="18">
@@ -10938,11 +10950,11 @@
         <v/>
       </c>
       <c r="Q40" s="18">
-        <f>IF($A40&lt;13,0,ROUND($G40*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
+        <f>IF($A40&lt;15,0,ROUND($G40*前提条件!$C$48*前提条件!$C$47*前提条件!$C$19,0))</f>
         <v/>
       </c>
       <c r="R40" s="18">
-        <f>IF($A40&lt;19,0,IF($A40&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
+        <f>IF($A40&lt;20,0,IF($A40&lt;=24,前提条件!$C$51,前提条件!$C$52)*前提条件!$C$50)</f>
         <v/>
       </c>
       <c r="S40" s="18">
@@ -11122,7 +11134,7 @@
       </c>
       <c r="N4" s="15" t="inlineStr">
         <is>
-          <t>ガイド売上</t>
+          <t>レシピ商品</t>
         </is>
       </c>
       <c r="O4" s="15" t="inlineStr">
@@ -11137,12 +11149,12 @@
       </c>
       <c r="Q4" s="15" t="inlineStr">
         <is>
-          <t>ｺﾝｼｪﾙｼﾞｭ</t>
+          <t>訪日商品</t>
         </is>
       </c>
       <c r="R4" s="15" t="inlineStr">
         <is>
-          <t>運用代行</t>
+          <t>予約代行</t>
         </is>
       </c>
       <c r="S4" s="15" t="inlineStr">
@@ -11152,7 +11164,7 @@
       </c>
       <c r="T4" s="15" t="inlineStr">
         <is>
-          <t>取材費</t>
+          <t>食材費</t>
         </is>
       </c>
       <c r="U4" s="15" t="inlineStr">
@@ -11246,7 +11258,7 @@
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>IF(OR($A5=5,$A5=9,$A5=15,$A5=21,$A5=27,$A5=33),ROUND(0*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A5=5,$A5=11,$A5=15,$A5=22,$A5=30),ROUND(0*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L5" s="16">
@@ -11270,11 +11282,11 @@
         <v/>
       </c>
       <c r="Q5" s="16">
-        <f>IF($A5&lt;13,0,ROUND($G5*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A5&lt;15,0,ROUND($G5*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R5" s="16">
-        <f>IF($A5&lt;19,0,IF($A5&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A5&lt;20,0,IF($A5&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S5" s="16">
@@ -11367,7 +11379,7 @@
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>IF(OR($A6=5,$A6=9,$A6=15,$A6=21,$A6=27,$A6=33),ROUND($I5*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A6=5,$A6=11,$A6=15,$A6=22,$A6=30),ROUND($I5*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L6" s="16">
@@ -11391,11 +11403,11 @@
         <v/>
       </c>
       <c r="Q6" s="16">
-        <f>IF($A6&lt;13,0,ROUND($G6*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A6&lt;15,0,ROUND($G6*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R6" s="16">
-        <f>IF($A6&lt;19,0,IF($A6&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A6&lt;20,0,IF($A6&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S6" s="16">
@@ -11488,7 +11500,7 @@
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>IF(OR($A7=5,$A7=9,$A7=15,$A7=21,$A7=27,$A7=33),ROUND($I6*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A7=5,$A7=11,$A7=15,$A7=22,$A7=30),ROUND($I6*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L7" s="16">
@@ -11512,11 +11524,11 @@
         <v/>
       </c>
       <c r="Q7" s="16">
-        <f>IF($A7&lt;13,0,ROUND($G7*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A7&lt;15,0,ROUND($G7*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R7" s="16">
-        <f>IF($A7&lt;19,0,IF($A7&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A7&lt;20,0,IF($A7&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S7" s="16">
@@ -11609,7 +11621,7 @@
         <v/>
       </c>
       <c r="K8" s="16">
-        <f>IF(OR($A8=5,$A8=9,$A8=15,$A8=21,$A8=27,$A8=33),ROUND($I7*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A8=5,$A8=11,$A8=15,$A8=22,$A8=30),ROUND($I7*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L8" s="16">
@@ -11633,11 +11645,11 @@
         <v/>
       </c>
       <c r="Q8" s="16">
-        <f>IF($A8&lt;13,0,ROUND($G8*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A8&lt;15,0,ROUND($G8*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R8" s="16">
-        <f>IF($A8&lt;19,0,IF($A8&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A8&lt;20,0,IF($A8&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S8" s="16">
@@ -11730,7 +11742,7 @@
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>IF(OR($A9=5,$A9=9,$A9=15,$A9=21,$A9=27,$A9=33),ROUND($I8*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A9=5,$A9=11,$A9=15,$A9=22,$A9=30),ROUND($I8*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L9" s="16">
@@ -11754,11 +11766,11 @@
         <v/>
       </c>
       <c r="Q9" s="16">
-        <f>IF($A9&lt;13,0,ROUND($G9*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A9&lt;15,0,ROUND($G9*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R9" s="16">
-        <f>IF($A9&lt;19,0,IF($A9&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A9&lt;20,0,IF($A9&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S9" s="16">
@@ -11851,7 +11863,7 @@
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>IF(OR($A10=5,$A10=9,$A10=15,$A10=21,$A10=27,$A10=33),ROUND($I9*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A10=5,$A10=11,$A10=15,$A10=22,$A10=30),ROUND($I9*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L10" s="16">
@@ -11875,11 +11887,11 @@
         <v/>
       </c>
       <c r="Q10" s="16">
-        <f>IF($A10&lt;13,0,ROUND($G10*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A10&lt;15,0,ROUND($G10*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R10" s="16">
-        <f>IF($A10&lt;19,0,IF($A10&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A10&lt;20,0,IF($A10&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S10" s="16">
@@ -11972,7 +11984,7 @@
         <v/>
       </c>
       <c r="K11" s="16">
-        <f>IF(OR($A11=5,$A11=9,$A11=15,$A11=21,$A11=27,$A11=33),ROUND($I10*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A11=5,$A11=11,$A11=15,$A11=22,$A11=30),ROUND($I10*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L11" s="16">
@@ -11996,11 +12008,11 @@
         <v/>
       </c>
       <c r="Q11" s="16">
-        <f>IF($A11&lt;13,0,ROUND($G11*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A11&lt;15,0,ROUND($G11*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R11" s="16">
-        <f>IF($A11&lt;19,0,IF($A11&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A11&lt;20,0,IF($A11&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S11" s="16">
@@ -12093,7 +12105,7 @@
         <v/>
       </c>
       <c r="K12" s="16">
-        <f>IF(OR($A12=5,$A12=9,$A12=15,$A12=21,$A12=27,$A12=33),ROUND($I11*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A12=5,$A12=11,$A12=15,$A12=22,$A12=30),ROUND($I11*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L12" s="16">
@@ -12117,11 +12129,11 @@
         <v/>
       </c>
       <c r="Q12" s="16">
-        <f>IF($A12&lt;13,0,ROUND($G12*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A12&lt;15,0,ROUND($G12*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R12" s="16">
-        <f>IF($A12&lt;19,0,IF($A12&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A12&lt;20,0,IF($A12&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S12" s="16">
@@ -12214,7 +12226,7 @@
         <v/>
       </c>
       <c r="K13" s="16">
-        <f>IF(OR($A13=5,$A13=9,$A13=15,$A13=21,$A13=27,$A13=33),ROUND($I12*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A13=5,$A13=11,$A13=15,$A13=22,$A13=30),ROUND($I12*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L13" s="16">
@@ -12238,11 +12250,11 @@
         <v/>
       </c>
       <c r="Q13" s="16">
-        <f>IF($A13&lt;13,0,ROUND($G13*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A13&lt;15,0,ROUND($G13*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R13" s="16">
-        <f>IF($A13&lt;19,0,IF($A13&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A13&lt;20,0,IF($A13&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S13" s="16">
@@ -12335,7 +12347,7 @@
         <v/>
       </c>
       <c r="K14" s="16">
-        <f>IF(OR($A14=5,$A14=9,$A14=15,$A14=21,$A14=27,$A14=33),ROUND($I13*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A14=5,$A14=11,$A14=15,$A14=22,$A14=30),ROUND($I13*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L14" s="16">
@@ -12359,11 +12371,11 @@
         <v/>
       </c>
       <c r="Q14" s="16">
-        <f>IF($A14&lt;13,0,ROUND($G14*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A14&lt;15,0,ROUND($G14*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R14" s="16">
-        <f>IF($A14&lt;19,0,IF($A14&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A14&lt;20,0,IF($A14&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S14" s="16">
@@ -12456,7 +12468,7 @@
         <v/>
       </c>
       <c r="K15" s="16">
-        <f>IF(OR($A15=5,$A15=9,$A15=15,$A15=21,$A15=27,$A15=33),ROUND($I14*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A15=5,$A15=11,$A15=15,$A15=22,$A15=30),ROUND($I14*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L15" s="16">
@@ -12480,11 +12492,11 @@
         <v/>
       </c>
       <c r="Q15" s="16">
-        <f>IF($A15&lt;13,0,ROUND($G15*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A15&lt;15,0,ROUND($G15*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R15" s="16">
-        <f>IF($A15&lt;19,0,IF($A15&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A15&lt;20,0,IF($A15&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S15" s="16">
@@ -12577,7 +12589,7 @@
         <v/>
       </c>
       <c r="K16" s="18">
-        <f>IF(OR($A16=5,$A16=9,$A16=15,$A16=21,$A16=27,$A16=33),ROUND($I15*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A16=5,$A16=11,$A16=15,$A16=22,$A16=30),ROUND($I15*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L16" s="18">
@@ -12601,11 +12613,11 @@
         <v/>
       </c>
       <c r="Q16" s="18">
-        <f>IF($A16&lt;13,0,ROUND($G16*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A16&lt;15,0,ROUND($G16*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R16" s="18">
-        <f>IF($A16&lt;19,0,IF($A16&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A16&lt;20,0,IF($A16&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S16" s="18">
@@ -12698,7 +12710,7 @@
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>IF(OR($A17=5,$A17=9,$A17=15,$A17=21,$A17=27,$A17=33),ROUND($I16*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A17=5,$A17=11,$A17=15,$A17=22,$A17=30),ROUND($I16*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L17" s="16">
@@ -12722,11 +12734,11 @@
         <v/>
       </c>
       <c r="Q17" s="16">
-        <f>IF($A17&lt;13,0,ROUND($G17*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A17&lt;15,0,ROUND($G17*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R17" s="16">
-        <f>IF($A17&lt;19,0,IF($A17&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A17&lt;20,0,IF($A17&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S17" s="16">
@@ -12819,7 +12831,7 @@
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>IF(OR($A18=5,$A18=9,$A18=15,$A18=21,$A18=27,$A18=33),ROUND($I17*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A18=5,$A18=11,$A18=15,$A18=22,$A18=30),ROUND($I17*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L18" s="16">
@@ -12843,11 +12855,11 @@
         <v/>
       </c>
       <c r="Q18" s="16">
-        <f>IF($A18&lt;13,0,ROUND($G18*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A18&lt;15,0,ROUND($G18*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R18" s="16">
-        <f>IF($A18&lt;19,0,IF($A18&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A18&lt;20,0,IF($A18&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S18" s="16">
@@ -12940,7 +12952,7 @@
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>IF(OR($A19=5,$A19=9,$A19=15,$A19=21,$A19=27,$A19=33),ROUND($I18*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A19=5,$A19=11,$A19=15,$A19=22,$A19=30),ROUND($I18*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L19" s="16">
@@ -12964,11 +12976,11 @@
         <v/>
       </c>
       <c r="Q19" s="16">
-        <f>IF($A19&lt;13,0,ROUND($G19*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A19&lt;15,0,ROUND($G19*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R19" s="16">
-        <f>IF($A19&lt;19,0,IF($A19&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A19&lt;20,0,IF($A19&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S19" s="16">
@@ -13061,7 +13073,7 @@
         <v/>
       </c>
       <c r="K20" s="16">
-        <f>IF(OR($A20=5,$A20=9,$A20=15,$A20=21,$A20=27,$A20=33),ROUND($I19*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A20=5,$A20=11,$A20=15,$A20=22,$A20=30),ROUND($I19*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L20" s="16">
@@ -13085,11 +13097,11 @@
         <v/>
       </c>
       <c r="Q20" s="16">
-        <f>IF($A20&lt;13,0,ROUND($G20*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A20&lt;15,0,ROUND($G20*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R20" s="16">
-        <f>IF($A20&lt;19,0,IF($A20&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A20&lt;20,0,IF($A20&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S20" s="16">
@@ -13182,7 +13194,7 @@
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>IF(OR($A21=5,$A21=9,$A21=15,$A21=21,$A21=27,$A21=33),ROUND($I20*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A21=5,$A21=11,$A21=15,$A21=22,$A21=30),ROUND($I20*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L21" s="16">
@@ -13206,11 +13218,11 @@
         <v/>
       </c>
       <c r="Q21" s="16">
-        <f>IF($A21&lt;13,0,ROUND($G21*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A21&lt;15,0,ROUND($G21*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R21" s="16">
-        <f>IF($A21&lt;19,0,IF($A21&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A21&lt;20,0,IF($A21&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S21" s="16">
@@ -13303,7 +13315,7 @@
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>IF(OR($A22=5,$A22=9,$A22=15,$A22=21,$A22=27,$A22=33),ROUND($I21*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A22=5,$A22=11,$A22=15,$A22=22,$A22=30),ROUND($I21*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L22" s="16">
@@ -13327,11 +13339,11 @@
         <v/>
       </c>
       <c r="Q22" s="16">
-        <f>IF($A22&lt;13,0,ROUND($G22*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A22&lt;15,0,ROUND($G22*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R22" s="16">
-        <f>IF($A22&lt;19,0,IF($A22&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A22&lt;20,0,IF($A22&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S22" s="16">
@@ -13424,7 +13436,7 @@
         <v/>
       </c>
       <c r="K23" s="16">
-        <f>IF(OR($A23=5,$A23=9,$A23=15,$A23=21,$A23=27,$A23=33),ROUND($I22*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A23=5,$A23=11,$A23=15,$A23=22,$A23=30),ROUND($I22*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L23" s="16">
@@ -13448,11 +13460,11 @@
         <v/>
       </c>
       <c r="Q23" s="16">
-        <f>IF($A23&lt;13,0,ROUND($G23*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A23&lt;15,0,ROUND($G23*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R23" s="16">
-        <f>IF($A23&lt;19,0,IF($A23&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A23&lt;20,0,IF($A23&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S23" s="16">
@@ -13545,7 +13557,7 @@
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>IF(OR($A24=5,$A24=9,$A24=15,$A24=21,$A24=27,$A24=33),ROUND($I23*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A24=5,$A24=11,$A24=15,$A24=22,$A24=30),ROUND($I23*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L24" s="16">
@@ -13569,11 +13581,11 @@
         <v/>
       </c>
       <c r="Q24" s="16">
-        <f>IF($A24&lt;13,0,ROUND($G24*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A24&lt;15,0,ROUND($G24*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R24" s="16">
-        <f>IF($A24&lt;19,0,IF($A24&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A24&lt;20,0,IF($A24&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S24" s="16">
@@ -13666,7 +13678,7 @@
         <v/>
       </c>
       <c r="K25" s="16">
-        <f>IF(OR($A25=5,$A25=9,$A25=15,$A25=21,$A25=27,$A25=33),ROUND($I24*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A25=5,$A25=11,$A25=15,$A25=22,$A25=30),ROUND($I24*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L25" s="16">
@@ -13690,11 +13702,11 @@
         <v/>
       </c>
       <c r="Q25" s="16">
-        <f>IF($A25&lt;13,0,ROUND($G25*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A25&lt;15,0,ROUND($G25*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R25" s="16">
-        <f>IF($A25&lt;19,0,IF($A25&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A25&lt;20,0,IF($A25&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S25" s="16">
@@ -13787,7 +13799,7 @@
         <v/>
       </c>
       <c r="K26" s="16">
-        <f>IF(OR($A26=5,$A26=9,$A26=15,$A26=21,$A26=27,$A26=33),ROUND($I25*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A26=5,$A26=11,$A26=15,$A26=22,$A26=30),ROUND($I25*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L26" s="16">
@@ -13811,11 +13823,11 @@
         <v/>
       </c>
       <c r="Q26" s="16">
-        <f>IF($A26&lt;13,0,ROUND($G26*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A26&lt;15,0,ROUND($G26*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R26" s="16">
-        <f>IF($A26&lt;19,0,IF($A26&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A26&lt;20,0,IF($A26&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S26" s="16">
@@ -13908,7 +13920,7 @@
         <v/>
       </c>
       <c r="K27" s="16">
-        <f>IF(OR($A27=5,$A27=9,$A27=15,$A27=21,$A27=27,$A27=33),ROUND($I26*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A27=5,$A27=11,$A27=15,$A27=22,$A27=30),ROUND($I26*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L27" s="16">
@@ -13932,11 +13944,11 @@
         <v/>
       </c>
       <c r="Q27" s="16">
-        <f>IF($A27&lt;13,0,ROUND($G27*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A27&lt;15,0,ROUND($G27*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R27" s="16">
-        <f>IF($A27&lt;19,0,IF($A27&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A27&lt;20,0,IF($A27&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S27" s="16">
@@ -14029,7 +14041,7 @@
         <v/>
       </c>
       <c r="K28" s="18">
-        <f>IF(OR($A28=5,$A28=9,$A28=15,$A28=21,$A28=27,$A28=33),ROUND($I27*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A28=5,$A28=11,$A28=15,$A28=22,$A28=30),ROUND($I27*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L28" s="18">
@@ -14053,11 +14065,11 @@
         <v/>
       </c>
       <c r="Q28" s="18">
-        <f>IF($A28&lt;13,0,ROUND($G28*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A28&lt;15,0,ROUND($G28*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R28" s="18">
-        <f>IF($A28&lt;19,0,IF($A28&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A28&lt;20,0,IF($A28&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S28" s="18">
@@ -14150,7 +14162,7 @@
         <v/>
       </c>
       <c r="K29" s="16">
-        <f>IF(OR($A29=5,$A29=9,$A29=15,$A29=21,$A29=27,$A29=33),ROUND($I28*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A29=5,$A29=11,$A29=15,$A29=22,$A29=30),ROUND($I28*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L29" s="16">
@@ -14174,11 +14186,11 @@
         <v/>
       </c>
       <c r="Q29" s="16">
-        <f>IF($A29&lt;13,0,ROUND($G29*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A29&lt;15,0,ROUND($G29*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R29" s="16">
-        <f>IF($A29&lt;19,0,IF($A29&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A29&lt;20,0,IF($A29&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S29" s="16">
@@ -14271,7 +14283,7 @@
         <v/>
       </c>
       <c r="K30" s="16">
-        <f>IF(OR($A30=5,$A30=9,$A30=15,$A30=21,$A30=27,$A30=33),ROUND($I29*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A30=5,$A30=11,$A30=15,$A30=22,$A30=30),ROUND($I29*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L30" s="16">
@@ -14295,11 +14307,11 @@
         <v/>
       </c>
       <c r="Q30" s="16">
-        <f>IF($A30&lt;13,0,ROUND($G30*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A30&lt;15,0,ROUND($G30*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R30" s="16">
-        <f>IF($A30&lt;19,0,IF($A30&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A30&lt;20,0,IF($A30&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S30" s="16">
@@ -14392,7 +14404,7 @@
         <v/>
       </c>
       <c r="K31" s="16">
-        <f>IF(OR($A31=5,$A31=9,$A31=15,$A31=21,$A31=27,$A31=33),ROUND($I30*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A31=5,$A31=11,$A31=15,$A31=22,$A31=30),ROUND($I30*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L31" s="16">
@@ -14416,11 +14428,11 @@
         <v/>
       </c>
       <c r="Q31" s="16">
-        <f>IF($A31&lt;13,0,ROUND($G31*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A31&lt;15,0,ROUND($G31*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R31" s="16">
-        <f>IF($A31&lt;19,0,IF($A31&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A31&lt;20,0,IF($A31&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S31" s="16">
@@ -14513,7 +14525,7 @@
         <v/>
       </c>
       <c r="K32" s="16">
-        <f>IF(OR($A32=5,$A32=9,$A32=15,$A32=21,$A32=27,$A32=33),ROUND($I31*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A32=5,$A32=11,$A32=15,$A32=22,$A32=30),ROUND($I31*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L32" s="16">
@@ -14537,11 +14549,11 @@
         <v/>
       </c>
       <c r="Q32" s="16">
-        <f>IF($A32&lt;13,0,ROUND($G32*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A32&lt;15,0,ROUND($G32*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R32" s="16">
-        <f>IF($A32&lt;19,0,IF($A32&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A32&lt;20,0,IF($A32&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S32" s="16">
@@ -14634,7 +14646,7 @@
         <v/>
       </c>
       <c r="K33" s="16">
-        <f>IF(OR($A33=5,$A33=9,$A33=15,$A33=21,$A33=27,$A33=33),ROUND($I32*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A33=5,$A33=11,$A33=15,$A33=22,$A33=30),ROUND($I32*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L33" s="16">
@@ -14658,11 +14670,11 @@
         <v/>
       </c>
       <c r="Q33" s="16">
-        <f>IF($A33&lt;13,0,ROUND($G33*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A33&lt;15,0,ROUND($G33*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R33" s="16">
-        <f>IF($A33&lt;19,0,IF($A33&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A33&lt;20,0,IF($A33&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S33" s="16">
@@ -14755,7 +14767,7 @@
         <v/>
       </c>
       <c r="K34" s="16">
-        <f>IF(OR($A34=5,$A34=9,$A34=15,$A34=21,$A34=27,$A34=33),ROUND($I33*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A34=5,$A34=11,$A34=15,$A34=22,$A34=30),ROUND($I33*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L34" s="16">
@@ -14779,11 +14791,11 @@
         <v/>
       </c>
       <c r="Q34" s="16">
-        <f>IF($A34&lt;13,0,ROUND($G34*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A34&lt;15,0,ROUND($G34*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R34" s="16">
-        <f>IF($A34&lt;19,0,IF($A34&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A34&lt;20,0,IF($A34&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S34" s="16">
@@ -14876,7 +14888,7 @@
         <v/>
       </c>
       <c r="K35" s="16">
-        <f>IF(OR($A35=5,$A35=9,$A35=15,$A35=21,$A35=27,$A35=33),ROUND($I34*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A35=5,$A35=11,$A35=15,$A35=22,$A35=30),ROUND($I34*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L35" s="16">
@@ -14900,11 +14912,11 @@
         <v/>
       </c>
       <c r="Q35" s="16">
-        <f>IF($A35&lt;13,0,ROUND($G35*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A35&lt;15,0,ROUND($G35*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R35" s="16">
-        <f>IF($A35&lt;19,0,IF($A35&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A35&lt;20,0,IF($A35&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S35" s="16">
@@ -14997,7 +15009,7 @@
         <v/>
       </c>
       <c r="K36" s="16">
-        <f>IF(OR($A36=5,$A36=9,$A36=15,$A36=21,$A36=27,$A36=33),ROUND($I35*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A36=5,$A36=11,$A36=15,$A36=22,$A36=30),ROUND($I35*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L36" s="16">
@@ -15021,11 +15033,11 @@
         <v/>
       </c>
       <c r="Q36" s="16">
-        <f>IF($A36&lt;13,0,ROUND($G36*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A36&lt;15,0,ROUND($G36*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R36" s="16">
-        <f>IF($A36&lt;19,0,IF($A36&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A36&lt;20,0,IF($A36&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S36" s="16">
@@ -15118,7 +15130,7 @@
         <v/>
       </c>
       <c r="K37" s="16">
-        <f>IF(OR($A37=5,$A37=9,$A37=15,$A37=21,$A37=27,$A37=33),ROUND($I36*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A37=5,$A37=11,$A37=15,$A37=22,$A37=30),ROUND($I36*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L37" s="16">
@@ -15142,11 +15154,11 @@
         <v/>
       </c>
       <c r="Q37" s="16">
-        <f>IF($A37&lt;13,0,ROUND($G37*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A37&lt;15,0,ROUND($G37*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R37" s="16">
-        <f>IF($A37&lt;19,0,IF($A37&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A37&lt;20,0,IF($A37&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S37" s="16">
@@ -15239,7 +15251,7 @@
         <v/>
       </c>
       <c r="K38" s="16">
-        <f>IF(OR($A38=5,$A38=9,$A38=15,$A38=21,$A38=27,$A38=33),ROUND($I37*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A38=5,$A38=11,$A38=15,$A38=22,$A38=30),ROUND($I37*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L38" s="16">
@@ -15263,11 +15275,11 @@
         <v/>
       </c>
       <c r="Q38" s="16">
-        <f>IF($A38&lt;13,0,ROUND($G38*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A38&lt;15,0,ROUND($G38*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R38" s="16">
-        <f>IF($A38&lt;19,0,IF($A38&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A38&lt;20,0,IF($A38&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S38" s="16">
@@ -15360,7 +15372,7 @@
         <v/>
       </c>
       <c r="K39" s="16">
-        <f>IF(OR($A39=5,$A39=9,$A39=15,$A39=21,$A39=27,$A39=33),ROUND($I38*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A39=5,$A39=11,$A39=15,$A39=22,$A39=30),ROUND($I38*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L39" s="16">
@@ -15384,11 +15396,11 @@
         <v/>
       </c>
       <c r="Q39" s="16">
-        <f>IF($A39&lt;13,0,ROUND($G39*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A39&lt;15,0,ROUND($G39*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R39" s="16">
-        <f>IF($A39&lt;19,0,IF($A39&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A39&lt;20,0,IF($A39&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S39" s="16">
@@ -15481,7 +15493,7 @@
         <v/>
       </c>
       <c r="K40" s="18">
-        <f>IF(OR($A40=5,$A40=9,$A40=15,$A40=21,$A40=27,$A40=33),ROUND($I39*前提条件!$D$35,0),0)</f>
+        <f>IF(OR($A40=5,$A40=11,$A40=15,$A40=22,$A40=30),ROUND($I39*前提条件!$D$35,0),0)</f>
         <v/>
       </c>
       <c r="L40" s="18">
@@ -15505,11 +15517,11 @@
         <v/>
       </c>
       <c r="Q40" s="18">
-        <f>IF($A40&lt;13,0,ROUND($G40*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
+        <f>IF($A40&lt;15,0,ROUND($G40*前提条件!$D$48*前提条件!$D$47*前提条件!$D$19,0))</f>
         <v/>
       </c>
       <c r="R40" s="18">
-        <f>IF($A40&lt;19,0,IF($A40&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
+        <f>IF($A40&lt;20,0,IF($A40&lt;=24,前提条件!$D$51,前提条件!$D$52)*前提条件!$D$50)</f>
         <v/>
       </c>
       <c r="S40" s="18">
@@ -15572,7 +15584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15656,7 +15668,7 @@
     <row r="5">
       <c r="A5" s="21" t="inlineStr">
         <is>
-          <t>売上：ガイド販売</t>
+          <t>売上：レシピ商品</t>
         </is>
       </c>
       <c r="B5" s="22">
@@ -15785,7 +15797,7 @@
     <row r="8">
       <c r="A8" s="21" t="inlineStr">
         <is>
-          <t>売上：コンシェルジュ</t>
+          <t>売上：訪日商品</t>
         </is>
       </c>
       <c r="B8" s="22">
@@ -15828,7 +15840,7 @@
     <row r="9">
       <c r="A9" s="21" t="inlineStr">
         <is>
-          <t>売上：運用代行</t>
+          <t>売上：予約代行</t>
         </is>
       </c>
       <c r="B9" s="22">
@@ -16129,7 +16141,7 @@
     <row r="16">
       <c r="A16" s="21" t="inlineStr">
         <is>
-          <t>年間ガイド販売数</t>
+          <t>年間商品販売数</t>
         </is>
       </c>
       <c r="B16" s="22">
@@ -16200,104 +16212,111 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>・訪日セグメント比率は3ヶ月目に実測し、⑥の転換率に反映すること。10%未満なら⑥⑦を計画から外す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>・売上構成比が「ガイド販売のみ」に偏っている場合、事業は脆い。24ヶ月目時点で4層に分散していることを確認する。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>■ 検算値（独立実装による再計算結果・標準シナリオ）</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>上の表の「標準」列がこの値と一致すれば数式は正しく組まれています。前提条件を編集すると当然ずれます。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr"/>
-      <c r="B28" s="20" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="20" t="inlineStr"/>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>1年目</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>2年目</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>3年目</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
-        <is>
-          <t>年間売上</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="n">
-        <v>1620948</v>
-      </c>
-      <c r="C29" s="25" t="n">
-        <v>11354400</v>
-      </c>
-      <c r="D29" s="25" t="n">
-        <v>24623088</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t>年間営業利益</t>
+          <t>年間売上</t>
         </is>
       </c>
       <c r="B30" s="25" t="n">
-        <v>45104</v>
+        <v>2431524</v>
       </c>
       <c r="C30" s="25" t="n">
-        <v>7130460</v>
+        <v>12903300</v>
       </c>
       <c r="D30" s="25" t="n">
-        <v>17522778</v>
+        <v>22534656</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>期末フォロワー</t>
+          <t>年間営業利益</t>
         </is>
       </c>
       <c r="B31" s="25" t="n">
-        <v>33000</v>
+        <v>1112621</v>
       </c>
       <c r="C31" s="25" t="n">
-        <v>93000</v>
+        <v>8856691</v>
       </c>
       <c r="D31" s="25" t="n">
-        <v>165000</v>
+        <v>15783291</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
+          <t>期末フォロワー</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>33900</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>96300</v>
+      </c>
+      <c r="D32" s="25" t="n">
+        <v>171900</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
           <t>期末メールリスト</t>
         </is>
       </c>
-      <c r="B32" s="25" t="n">
-        <v>3116</v>
-      </c>
-      <c r="C32" s="25" t="n">
-        <v>9441</v>
-      </c>
-      <c r="D32" s="25" t="n">
-        <v>18059</v>
+      <c r="B33" s="25" t="n">
+        <v>3184</v>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>9678</v>
+      </c>
+      <c r="D33" s="25" t="n">
+        <v>18533</v>
       </c>
     </row>
   </sheetData>
